--- a/data/deudas/deudas.xlsx
+++ b/data/deudas/deudas.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,46 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Didi Karime</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D3" t="n">
+        <v>125</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>quincenal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
